--- a/Bugsheet.xlsx
+++ b/Bugsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sange\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52DF99C3-F246-43CD-95D8-7638B21D41F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C54C631-34B9-4254-AF17-3182E08B24DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-135" yWindow="-135" windowWidth="38670" windowHeight="21150" xr2:uid="{AF43AC71-B01E-46A9-A71E-2AF0148259BC}"/>
   </bookViews>
@@ -16,6 +16,10 @@
     <sheet name="Admin Portal Bugsheet" sheetId="1" r:id="rId1"/>
     <sheet name="User webpage" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'User webpage'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Admin Portal Bugsheet'!$A$1:$G$48</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="224">
   <si>
     <t>Testcase Description</t>
   </si>
@@ -573,9 +577,6 @@
 The "Tags" column on the main table is completely blank for all entries.</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -808,7 +809,29 @@
     <t>The screen responsiveness should be same for all the dimensions</t>
   </si>
   <si>
-    <t>The screen responsiveness reduces as the dimension increases</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The screen responsiveness reduces as the dimension increases
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screen Resolutions to check with : "2560 × 1440" and "3840 × 2160"</t>
+    </r>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
   <si>
     <t>Check the Course module by adding a course</t>
@@ -1221,6 +1244,9 @@
     <t>The 'Close' and 'Submit' buttons are not static/fixed; they scroll away with the question content, requiring the user to scroll back or to the very bottom/top to take action.</t>
   </si>
   <si>
+    <t>Still Open</t>
+  </si>
+  <si>
     <t>Check the Upload New Mains Test Script button in the mentorship dashboard</t>
   </si>
   <si>
@@ -1248,6 +1274,29 @@
   </si>
   <si>
     <t>The system making the user to join everytime on navigating to the mentorship courses</t>
+  </si>
+  <si>
+    <t>Check the take test option in mentor dashboard</t>
+  </si>
+  <si>
+    <t>1) Click on Sign in/Register and login
+2) Click on Mentorship
+3) Select one of the course and click join now
+4) Navigate to the card to take the test 
+5) Click on the "Go to Mains Test Series"</t>
+  </si>
+  <si>
+    <t>The system should open another popup to display the test window</t>
+  </si>
+  <si>
+    <t>The system now navigates to test series module</t>
+  </si>
+  <si>
+    <t>1) Click on Sign in/Register and login
+2) Click on Mentorship
+3) Select one of the course and click join now
+4) Navigate to the card to take the test 
+5) Click on the "Go to Prelims Test Series"</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1368,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1342,6 +1391,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
         <bgColor rgb="FFC00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1385,7 +1440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1423,14 +1478,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1466,8 +1524,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1104900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1510,8 +1568,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>971550</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>523875</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1562,8 +1620,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>2339523</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>354404</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>120089</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1606,8 +1664,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1981354</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>125730</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>579120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1651,8 +1709,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>2110740</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>701040</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>678180</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1696,8 +1754,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>2495872</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>743012</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>447737</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1740,8 +1798,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>2333919</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>714436</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>438211</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1832,7 +1890,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>2552700</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>914400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2188,6 +2246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA92AF0F-DDA1-425F-8BD7-0C6A2F27C8FE}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2223,7 +2282,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="101.25">
+    <row r="2" spans="1:7" ht="101.25" hidden="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2244,7 +2303,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="72.75">
+    <row r="3" spans="1:7" ht="72.75" hidden="1">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2264,7 +2323,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="101.25">
+    <row r="4" spans="1:7" ht="101.25" hidden="1">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -2284,7 +2343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="115.5">
+    <row r="5" spans="1:7" ht="115.5" hidden="1">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -2304,7 +2363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="130.5">
+    <row r="6" spans="1:7" ht="130.5" hidden="1">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,7 +2383,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="130.5">
+    <row r="7" spans="1:7" ht="130.5" hidden="1">
       <c r="A7" s="1" t="s">
         <v>29</v>
       </c>
@@ -2344,7 +2403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="159">
+    <row r="8" spans="1:7" ht="159" hidden="1">
       <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
@@ -2364,7 +2423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="101.25">
+    <row r="9" spans="1:7" ht="101.25" hidden="1">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -2384,7 +2443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="115.5">
+    <row r="10" spans="1:7" ht="115.5" hidden="1">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -2404,7 +2463,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="87">
+    <row r="11" spans="1:7" ht="87" hidden="1">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -2424,7 +2483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="115.5">
+    <row r="12" spans="1:7" ht="115.5" hidden="1">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -2444,7 +2503,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="115.5">
+    <row r="13" spans="1:7" ht="115.5" hidden="1">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -2464,7 +2523,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="72.75">
+    <row r="14" spans="1:7" ht="72.75" hidden="1">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -2484,7 +2543,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="72.75">
+    <row r="15" spans="1:7" ht="72.75" hidden="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -2507,7 +2566,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="87">
+    <row r="16" spans="1:7" ht="87" hidden="1">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -2527,7 +2586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="72.75">
+    <row r="17" spans="1:6" ht="72.75" hidden="1">
       <c r="A17" s="9" t="s">
         <v>54</v>
       </c>
@@ -2547,7 +2606,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="72.75">
+    <row r="18" spans="1:6" ht="72.75" hidden="1">
       <c r="A18" s="9" t="s">
         <v>56</v>
       </c>
@@ -2567,7 +2626,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="87">
+    <row r="19" spans="1:6" ht="87" hidden="1">
       <c r="A19" s="9" t="s">
         <v>58</v>
       </c>
@@ -2587,7 +2646,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="87">
+    <row r="20" spans="1:6" ht="87" hidden="1">
       <c r="A20" s="9" t="s">
         <v>60</v>
       </c>
@@ -2607,7 +2666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="87">
+    <row r="21" spans="1:6" ht="87" hidden="1">
       <c r="A21" s="10" t="s">
         <v>62</v>
       </c>
@@ -2627,7 +2686,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="43.5">
+    <row r="22" spans="1:6" ht="43.5" hidden="1">
       <c r="A22" s="1" t="s">
         <v>66</v>
       </c>
@@ -2647,7 +2706,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="72.75">
+    <row r="23" spans="1:6" ht="72.75" hidden="1">
       <c r="A23" s="9" t="s">
         <v>70</v>
       </c>
@@ -2667,7 +2726,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="72.75">
+    <row r="24" spans="1:6" ht="72.75" hidden="1">
       <c r="A24" s="10" t="s">
         <v>74</v>
       </c>
@@ -2687,7 +2746,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="72.75">
+    <row r="25" spans="1:6" ht="72.75" hidden="1">
       <c r="A25" s="10" t="s">
         <v>76</v>
       </c>
@@ -2721,18 +2780,18 @@
         <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="72.75" hidden="1">
+      <c r="A27" s="10" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="72.75">
-      <c r="A27" s="10" t="s">
+      <c r="B27" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>72</v>
@@ -2747,12 +2806,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="72.75">
+    <row r="28" spans="1:6" ht="72.75" hidden="1">
       <c r="A28" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>15</v>
@@ -2767,12 +2826,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="87">
+    <row r="29" spans="1:6" ht="87" hidden="1">
       <c r="A29" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>15</v>
@@ -2787,12 +2846,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="87">
+    <row r="30" spans="1:6" ht="87" hidden="1">
       <c r="A30" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>15</v>
@@ -2807,18 +2866,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="107.25" customHeight="1">
+    <row r="31" spans="1:6" ht="107.25" hidden="1" customHeight="1">
       <c r="A31" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>51</v>
@@ -2827,15 +2886,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="138" customHeight="1">
+    <row r="32" spans="1:6" ht="138" hidden="1" customHeight="1">
       <c r="A32" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>16</v>
@@ -2847,47 +2906,47 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="138" customHeight="1">
+    <row r="33" spans="1:7" ht="138" hidden="1" customHeight="1">
       <c r="A33" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="101.25">
+      <c r="A34" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="43.5">
-      <c r="A34" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="16" t="s">
         <v>102</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="101.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="101.25" hidden="1">
       <c r="A35" s="1" t="s">
         <v>104</v>
       </c>
@@ -2907,7 +2966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="101.25">
+    <row r="36" spans="1:7" ht="101.25" hidden="1">
       <c r="A36" s="1" t="s">
         <v>104</v>
       </c>
@@ -2930,7 +2989,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="87">
+    <row r="37" spans="1:7" ht="87" hidden="1">
       <c r="A37" s="1" t="s">
         <v>104</v>
       </c>
@@ -2951,7 +3010,7 @@
       </c>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" ht="87">
+    <row r="38" spans="1:7" ht="87" hidden="1">
       <c r="A38" s="1" t="s">
         <v>104</v>
       </c>
@@ -2972,7 +3031,7 @@
       </c>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" ht="101.25">
+    <row r="39" spans="1:7" ht="101.25" hidden="1">
       <c r="A39" s="1" t="s">
         <v>104</v>
       </c>
@@ -3007,14 +3066,14 @@
         <v>16</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>81</v>
+        <v>11</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>12</v>
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" ht="101.25">
+    <row r="41" spans="1:7" ht="101.25" hidden="1">
       <c r="A41" s="1" t="s">
         <v>104</v>
       </c>
@@ -3035,7 +3094,7 @@
       </c>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:7" ht="101.25">
+    <row r="42" spans="1:7" ht="101.25" hidden="1">
       <c r="A42" s="1" t="s">
         <v>104</v>
       </c>
@@ -3056,7 +3115,7 @@
       </c>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:7" ht="101.25">
+    <row r="43" spans="1:7" ht="101.25" hidden="1">
       <c r="A43" s="1" t="s">
         <v>104</v>
       </c>
@@ -3077,7 +3136,7 @@
       </c>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" ht="115.5">
+    <row r="44" spans="1:7" ht="115.5" hidden="1">
       <c r="A44" s="1" t="s">
         <v>104</v>
       </c>
@@ -3098,7 +3157,7 @@
       </c>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="1:7" ht="115.5">
+    <row r="45" spans="1:7" ht="115.5" hidden="1">
       <c r="A45" s="9" t="s">
         <v>54</v>
       </c>
@@ -3118,7 +3177,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="87">
+    <row r="46" spans="1:7" ht="87" hidden="1">
       <c r="A46" s="10" t="s">
         <v>76</v>
       </c>
@@ -3138,7 +3197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="72.75">
+    <row r="47" spans="1:7" ht="72.75" hidden="1">
       <c r="A47" s="10" t="s">
         <v>76</v>
       </c>
@@ -3158,7 +3217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="87">
+    <row r="48" spans="1:7" ht="87" hidden="1">
       <c r="A48" s="10" t="s">
         <v>76</v>
       </c>
@@ -3179,6 +3238,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G48" xr:uid="{EA92AF0F-DDA1-425F-8BD7-0C6A2F27C8FE}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Fail"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3186,7 +3252,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AD32A5-9065-4057-ACC5-DEF1EF66C778}">
-  <dimension ref="A1:H23"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.5703125" style="2" customWidth="1"/>
@@ -3224,7 +3291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="43.5">
+    <row r="2" spans="1:8" ht="43.5" hidden="1">
       <c r="A2" s="1" t="s">
         <v>132</v>
       </c>
@@ -3247,7 +3314,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="115.5">
+    <row r="3" spans="1:8" ht="115.5" hidden="1">
       <c r="A3" s="1" t="s">
         <v>137</v>
       </c>
@@ -3273,7 +3340,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="43.5">
+    <row r="4" spans="1:8" ht="43.5" hidden="1">
       <c r="A4" s="1" t="s">
         <v>137</v>
       </c>
@@ -3296,7 +3363,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="72.75">
+    <row r="5" spans="1:8" ht="72.75" hidden="1">
       <c r="A5" s="1" t="s">
         <v>145</v>
       </c>
@@ -3322,7 +3389,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="57.75">
+    <row r="6" spans="1:8" ht="57.75" hidden="1">
       <c r="A6" s="1" t="s">
         <v>137</v>
       </c>
@@ -3345,7 +3412,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="57.75">
+    <row r="7" spans="1:8" ht="57.75" hidden="1">
       <c r="A7" s="1" t="s">
         <v>153</v>
       </c>
@@ -3382,13 +3449,13 @@
         <v>160</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="87">
+        <v>11</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="87" hidden="1">
       <c r="A9" s="2" t="s">
         <v>161</v>
       </c>
@@ -3408,7 +3475,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="107.25" customHeight="1">
+    <row r="10" spans="1:8" ht="107.25" hidden="1" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>165</v>
       </c>
@@ -3428,7 +3495,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="57.75">
+    <row r="11" spans="1:8" ht="57.75" hidden="1">
       <c r="A11" s="1" t="s">
         <v>169</v>
       </c>
@@ -3448,7 +3515,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="57.75">
+    <row r="12" spans="1:8" ht="57.75" hidden="1">
       <c r="A12" s="1" t="s">
         <v>173</v>
       </c>
@@ -3468,7 +3535,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="87">
+    <row r="13" spans="1:8" ht="87" hidden="1">
       <c r="A13" s="1" t="s">
         <v>169</v>
       </c>
@@ -3488,7 +3555,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="72.75">
+    <row r="14" spans="1:8" ht="72.75" hidden="1">
       <c r="A14" s="1" t="s">
         <v>169</v>
       </c>
@@ -3508,7 +3575,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="57.75">
+    <row r="15" spans="1:8" ht="57.75" hidden="1">
       <c r="A15" s="1" t="s">
         <v>182</v>
       </c>
@@ -3542,13 +3609,13 @@
         <v>189</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="101.25">
+        <v>11</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="101.25" hidden="1">
       <c r="A17" s="1" t="s">
         <v>190</v>
       </c>
@@ -3568,7 +3635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="43.5">
+    <row r="18" spans="1:7" ht="43.5">
       <c r="A18" s="11" t="s">
         <v>194</v>
       </c>
@@ -3581,14 +3648,14 @@
       <c r="D18" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="87">
+      <c r="E18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="87">
       <c r="A19" s="11" t="s">
         <v>198</v>
       </c>
@@ -3601,14 +3668,14 @@
       <c r="D19" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="86.25" customHeight="1">
+      <c r="E19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="86.25" customHeight="1">
       <c r="A20" s="11" t="s">
         <v>202</v>
       </c>
@@ -3621,14 +3688,14 @@
       <c r="D20" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="74.25" customHeight="1">
+      <c r="E20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="74.25" customHeight="1">
       <c r="A21" s="11" t="s">
         <v>206</v>
       </c>
@@ -3641,54 +3708,104 @@
       <c r="D21" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="87">
+      <c r="F21" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="87">
       <c r="A22" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="57.75">
+      <c r="A23" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="115.5">
+      <c r="A24" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="57.75">
-      <c r="A23" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F24" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="115.5">
+      <c r="A25" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>81</v>
+      <c r="F25" s="14" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H23" xr:uid="{39AD32A5-9065-4057-ACC5-DEF1EF66C778}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Fail"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
